--- a/public/templates/process-docs/厂房普通紧固件连接工程检验批质量验收记录.xlsx
+++ b/public/templates/process-docs/厂房普通紧固件连接工程检验批质量验收记录.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">工程编号：</t>
   </si>
   <si>
-    <t xml:space="preserve">5028G01-0011</t>
+    <t xml:space="preserve">{{工程编号}}</t>
   </si>
   <si>
     <t xml:space="preserve">单位（子单位）工程名称</t>
@@ -142,13 +142,13 @@
     <t xml:space="preserve">总承包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工单位</t>
@@ -157,13 +157,13 @@
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包项目负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">施工执行标准名称及编号</t>
